--- a/data/trans_camb/IP2001-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP2001-Provincia-trans_camb.xlsx
@@ -614,7 +614,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,61; 7,56</t>
+          <t>-10,19; 6,94</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 17,95</t>
+          <t>-2,29; 17,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-12,81; 0,99</t>
+          <t>-14,35; 0,65</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 16,94</t>
+          <t>-2,87; 17,16</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,99; 13,22</t>
+          <t>-5,9; 13,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-15,0; -1,22</t>
+          <t>-14,71; -0,73</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 10,29</t>
+          <t>-3,88; 9,12</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 13,02</t>
+          <t>-0,75; 13,12</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-11,33; -1,65</t>
+          <t>-11,39; -1,48</t>
         </is>
       </c>
     </row>
@@ -783,54 +783,54 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-75,13; 205,74</t>
+          <t>-75,03; 183,57</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-17,5; 513,0</t>
+          <t>-22,76; 442,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 74,92</t>
+          <t>-100,0; 57,2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-27,51; 405,14</t>
+          <t>-35,19; 430,54</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-53,64; 338,22</t>
+          <t>-55,2; 361,79</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 64,18</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-30,56; 205,61</t>
+          <t>-36,15; 171,24</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-11,03; 269,12</t>
+          <t>-12,09; 260,27</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-92,17; -21,74</t>
+          <t>-91,98; -8,38</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 9,89</t>
+          <t>-5,93; 10,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,84; 2,24</t>
+          <t>-11,16; 2,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-16,43; -4,02</t>
+          <t>-17,2; -4,9</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-13,92; 2,61</t>
+          <t>-13,84; 2,74</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-17,46; -2,42</t>
+          <t>-17,42; -2,57</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-17,93; -3,27</t>
+          <t>-18,02; -2,8</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-8,13; 3,69</t>
+          <t>-7,89; 3,24</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-13,22; -2,58</t>
+          <t>-12,55; -2,2</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-15,96; -6,54</t>
+          <t>-15,66; -6,23</t>
         </is>
       </c>
     </row>
@@ -999,54 +999,54 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-37,06; 105,36</t>
+          <t>-37,8; 123,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-71,06; 31,19</t>
+          <t>-68,38; 39,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-96,56; -41,99</t>
+          <t>-97,2; -49,54</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-61,45; 20,7</t>
+          <t>-62,29; 23,67</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-78,1; -14,14</t>
+          <t>-79,21; -17,88</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-82,47; -18,33</t>
+          <t>-81,92; -8,11</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-45,13; 28,77</t>
+          <t>-42,49; 28,57</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-69,26; -17,56</t>
+          <t>-68,38; -15,33</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-85,59; -43,23</t>
+          <t>-85,35; -43,64</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,14; 12,07</t>
+          <t>0,12; 13,48</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 9,21</t>
+          <t>-2,87; 8,08</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,86; 13,97</t>
+          <t>0,67; 13,35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 8,99</t>
+          <t>-2,84; 9,08</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,82; 3,66</t>
+          <t>-4,77; 3,71</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 13,98</t>
+          <t>-0,16; 16,37</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 8,3</t>
+          <t>-0,12; 8,07</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 4,41</t>
+          <t>-2,74; 4,33</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,28; 11,12</t>
+          <t>1,37; 11,22</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-46,56; —</t>
+          <t>-47,55; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-30,38; —</t>
+          <t>-39,92; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
+          <t>-82,23; —</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-56,89; 1717,8</t>
+          <t>-49,04; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-19,77; 764,63</t>
+          <t>-21,13; 739,8</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-73,57; 450,86</t>
+          <t>-76,54; 382,18</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,39; 991,31</t>
+          <t>14,22; 940,14</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 13,63</t>
+          <t>-0,85; 14,36</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,9; 23,25</t>
+          <t>6,13; 23,53</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,09; 5,52</t>
+          <t>-5,77; 6,44</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,22; 14,84</t>
+          <t>-0,33; 14,4</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,81; 23,58</t>
+          <t>6,44; 24,12</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,82; 9,54</t>
+          <t>-4,66; 10,29</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,94; 12,31</t>
+          <t>2,17; 12,4</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8,49; 20,46</t>
+          <t>8,69; 21,2</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 5,47</t>
+          <t>-3,99; 5,66</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-28,55; 567,98</t>
+          <t>-23,77; 585,54</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>45,56; 978,11</t>
+          <t>53,22; 987,01</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-84,47; 242,44</t>
+          <t>-78,35; 347,79</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-19,27; 1052,91</t>
+          <t>-18,15; 1083,7</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>58,13; 1713,67</t>
+          <t>58,18; 1766,25</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 719,86</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,56; 437,76</t>
+          <t>29,76; 516,93</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>115,05; 788,71</t>
+          <t>124,61; 841,91</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-67,57; 196,86</t>
+          <t>-65,85; 217,87</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-14,49; 15,24</t>
+          <t>-14,96; 14,67</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-24,05; 3,01</t>
+          <t>-24,9; 2,65</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-27,47; -2,16</t>
+          <t>-27,8; -2,74</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-10,69; 11,03</t>
+          <t>-9,87; 12,48</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 18,93</t>
+          <t>-3,93; 19,37</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-6,65; 14,84</t>
+          <t>-6,33; 15,35</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-8,42; 10,89</t>
+          <t>-9,24; 9,52</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-10,75; 7,93</t>
+          <t>-10,4; 7,69</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-13,41; 3,23</t>
+          <t>-14,16; 2,62</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-50,93; 113,27</t>
+          <t>-52,66; 108,95</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-81,43; 29,9</t>
+          <t>-79,91; 28,1</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-90,34; -7,83</t>
+          <t>-90,76; 0,26</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-72,13; 221,39</t>
+          <t>-65,64; 315,72</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-41,24; 395,05</t>
+          <t>-32,38; 422,11</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-46,02; 368,38</t>
+          <t>-47,43; 348,45</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-41,81; 100,41</t>
+          <t>-46,14; 83,79</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-51,26; 74,72</t>
+          <t>-49,76; 76,35</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-65,66; 31,78</t>
+          <t>-69,94; 22,55</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 11,82</t>
+          <t>-1,53; 11,79</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 14,6</t>
+          <t>-0,69; 13,76</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 9,08</t>
+          <t>-2,89; 10,05</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6,84; 24,31</t>
+          <t>6,88; 24,23</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 4,77</t>
+          <t>-2,17; 4,81</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 7,18</t>
+          <t>-1,09; 7,43</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,52; 16,52</t>
+          <t>4,04; 15,76</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 7,55</t>
+          <t>-0,54; 8,02</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 6,29</t>
+          <t>-1,57; 5,92</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-65,33; —</t>
+          <t>-48,65; —</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1893,24 +1893,24 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>69,31; 2339,3</t>
+          <t>71,72; 2792,17</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-62,3; 1187,22</t>
+          <t>-49,03; 1489,42</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-76,5; 923,54</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 5,93</t>
+          <t>-3,07; 6,06</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 5,31</t>
+          <t>-3,29; 5,42</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 8,14</t>
+          <t>-1,43; 7,78</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 7,69</t>
+          <t>-3,0; 7,83</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 6,99</t>
+          <t>-3,19; 6,36</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 10,18</t>
+          <t>-0,93; 10,57</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 5,68</t>
+          <t>-1,91; 5,24</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 4,75</t>
+          <t>-2,02; 5,25</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 7,87</t>
+          <t>0,38; 8,28</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-59,9; 292,45</t>
+          <t>-53,67; 295,46</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-57,38; 283,81</t>
+          <t>-53,19; 254,17</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-34,27; 446,63</t>
+          <t>-30,72; 403,13</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-43,56; 212,48</t>
+          <t>-41,04; 209,19</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-43,34; 215,93</t>
+          <t>-44,49; 185,3</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-19,93; 276,2</t>
+          <t>-16,01; 284,78</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-29,95; 166,99</t>
+          <t>-29,47; 150,24</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-28,31; 143,92</t>
+          <t>-33,84; 150,62</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 231,76</t>
+          <t>0,69; 224,39</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-10,73; 0,02</t>
+          <t>-10,69; 0,1</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-5,85; 6,24</t>
+          <t>-6,03; 6,4</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-15,56; -5,94</t>
+          <t>-15,23; -5,81</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-8,34; 0,94</t>
+          <t>-7,94; 1,22</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 8,1</t>
+          <t>-2,94; 7,81</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-12,15; -3,81</t>
+          <t>-11,8; -3,88</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-7,84; -0,77</t>
+          <t>-7,9; -0,63</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 5,31</t>
+          <t>-2,81; 5,71</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-12,35; -5,83</t>
+          <t>-12,27; -6,14</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-67,49; 11,74</t>
+          <t>-69,09; 2,98</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-37,55; 70,55</t>
+          <t>-37,29; 71,08</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-96,17; -52,52</t>
+          <t>-96,08; -51,5</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-73,12; 18,49</t>
+          <t>-68,86; 22,36</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-31,2; 129,77</t>
+          <t>-27,1; 123,67</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-96,52; -46,18</t>
+          <t>-96,41; -42,19</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-60,5; -6,51</t>
+          <t>-60,89; -4,39</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-19,88; 60,71</t>
+          <t>-21,38; 63,39</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-93,64; -60,63</t>
+          <t>-94,19; -62,81</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 3,33</t>
+          <t>-1,45; 3,56</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 4,59</t>
+          <t>-0,72; 4,6</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-6,11; -1,95</t>
+          <t>-6,17; -1,59</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 3,8</t>
+          <t>-1,31; 3,78</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 4,16</t>
+          <t>-0,65; 4,34</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 0,43</t>
+          <t>-4,45; 0,32</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 3,0</t>
+          <t>-0,66; 3,03</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>0,03; 3,81</t>
+          <t>0,03; 3,66</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-4,55; -1,25</t>
+          <t>-4,53; -1,35</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-16,21; 45,07</t>
+          <t>-15,29; 50,27</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-7,86; 62,88</t>
+          <t>-8,4; 61,07</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-64,77; -25,68</t>
+          <t>-64,09; -21,4</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-12,22; 54,55</t>
+          <t>-14,33; 55,0</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-8,08; 60,9</t>
+          <t>-7,84; 65,34</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-45,65; 7,15</t>
+          <t>-46,15; 5,79</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-7,15; 40,73</t>
+          <t>-6,94; 40,94</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>1,32; 51,64</t>
+          <t>-0,07; 49,71</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-49,76; -15,91</t>
+          <t>-50,1; -17,91</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP2001-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP2001-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-10,19; 6,94</t>
+          <t>-9,0; 7,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 17,81</t>
+          <t>-2,43; 18,72</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-14,35; 0,65</t>
+          <t>-13,82; 1,44</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 17,16</t>
+          <t>-2,49; 16,44</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 13,36</t>
+          <t>-5,36; 13,19</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-14,71; -0,73</t>
+          <t>-14,62; -1,19</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 9,12</t>
+          <t>-3,56; 9,88</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 13,12</t>
+          <t>-1,55; 12,09</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-11,39; -1,48</t>
+          <t>-11,96; -1,45</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-75,03; 183,57</t>
+          <t>-74,9; 278,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-22,76; 442,51</t>
+          <t>-25,54; 554,86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 57,2</t>
+          <t>-100,0; 122,31</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-35,19; 430,54</t>
+          <t>-27,51; 486,42</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-55,2; 361,79</t>
+          <t>-49,46; 415,09</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 56,21</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-36,15; 171,24</t>
+          <t>-34,68; 195,78</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-12,09; 260,27</t>
+          <t>-17,85; 228,74</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-91,98; -8,38</t>
+          <t>-92,12; -9,56</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,93; 10,44</t>
+          <t>-6,67; 9,9</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,16; 2,66</t>
+          <t>-12,14; 2,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-17,2; -4,9</t>
+          <t>-16,66; -4,61</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-13,84; 2,74</t>
+          <t>-12,75; 3,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-17,42; -2,57</t>
+          <t>-17,44; -3,08</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-18,02; -2,8</t>
+          <t>-18,33; -3,03</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-7,89; 3,24</t>
+          <t>-7,89; 3,49</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-12,55; -2,2</t>
+          <t>-12,57; -1,73</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-15,66; -6,23</t>
+          <t>-16,48; -6,08</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-37,8; 123,8</t>
+          <t>-41,84; 115,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-68,38; 39,08</t>
+          <t>-73,07; 33,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-97,2; -49,54</t>
+          <t>-96,88; -49,32</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-62,29; 23,67</t>
+          <t>-58,02; 30,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-79,21; -17,88</t>
+          <t>-77,93; -18,37</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-81,92; -8,11</t>
+          <t>-83,38; -12,51</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-42,49; 28,57</t>
+          <t>-42,26; 29,4</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-68,38; -15,33</t>
+          <t>-67,6; -12,87</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-85,35; -43,64</t>
+          <t>-86,5; -42,68</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,12; 13,48</t>
+          <t>-0,43; 12,86</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 8,08</t>
+          <t>-2,18; 8,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,67; 13,35</t>
+          <t>0,64; 13,17</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 9,08</t>
+          <t>-2,88; 8,94</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 3,71</t>
+          <t>-4,82; 4,39</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 16,37</t>
+          <t>-0,76; 14,32</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 8,07</t>
+          <t>-0,05; 8,62</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 4,33</t>
+          <t>-2,7; 4,35</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,37; 11,22</t>
+          <t>1,48; 11,3</t>
         </is>
       </c>
     </row>
@@ -1215,24 +1215,24 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-47,55; —</t>
+          <t>-49,68; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>-100,0; —</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>-51,02; —</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>-39,92; —</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>-82,23; —</t>
-        </is>
-      </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -1240,22 +1240,22 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-49,04; —</t>
+          <t>-43,87; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-21,13; 739,8</t>
+          <t>-24,08; 897,82</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-76,54; 382,18</t>
+          <t>-76,26; 487,65</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>14,22; 940,14</t>
+          <t>14,08; 1064,8</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 14,36</t>
+          <t>-0,68; 14,54</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,13; 23,53</t>
+          <t>6,33; 24,65</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,77; 6,44</t>
+          <t>-5,91; 6,54</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 14,4</t>
+          <t>-0,35; 14,48</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,44; 24,12</t>
+          <t>5,3; 22,64</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,66; 10,29</t>
+          <t>-5,0; 10,37</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,17; 12,4</t>
+          <t>1,71; 11,9</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8,69; 21,2</t>
+          <t>8,86; 20,71</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 5,66</t>
+          <t>-3,64; 5,44</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-23,77; 585,54</t>
+          <t>-27,98; 586,42</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>53,22; 987,01</t>
+          <t>52,56; 961,94</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-78,35; 347,79</t>
+          <t>-81,4; 327,28</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-18,15; 1083,7</t>
+          <t>-21,23; 986,63</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>58,18; 1766,25</t>
+          <t>56,81; 1643,8</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 676,21</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,76; 516,93</t>
+          <t>11,27; 391,94</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>124,61; 841,91</t>
+          <t>127,39; 766,79</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-65,85; 217,87</t>
+          <t>-63,14; 183,14</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-14,96; 14,67</t>
+          <t>-16,18; 15,2</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-24,9; 2,65</t>
+          <t>-24,36; 2,74</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-27,8; -2,74</t>
+          <t>-28,73; -2,93</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-9,87; 12,48</t>
+          <t>-10,0; 12,23</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 19,37</t>
+          <t>-3,07; 20,3</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-6,33; 15,35</t>
+          <t>-7,18; 15,0</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-9,24; 9,52</t>
+          <t>-8,81; 10,26</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-10,4; 7,69</t>
+          <t>-9,53; 8,1</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-14,16; 2,62</t>
+          <t>-14,0; 3,06</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-52,66; 108,95</t>
+          <t>-54,51; 108,89</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-79,91; 28,1</t>
+          <t>-81,8; 27,81</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-90,76; 0,26</t>
+          <t>-91,0; -11,33</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-65,64; 315,72</t>
+          <t>-70,53; 251,46</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-32,38; 422,11</t>
+          <t>-29,64; 400,78</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-47,43; 348,45</t>
+          <t>-52,14; 320,87</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-46,14; 83,79</t>
+          <t>-44,46; 94,08</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-49,76; 76,35</t>
+          <t>-48,15; 78,41</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-69,94; 22,55</t>
+          <t>-68,03; 30,33</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 11,79</t>
+          <t>-1,86; 11,0</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 13,76</t>
+          <t>-0,37; 15,07</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 10,05</t>
+          <t>-2,46; 10,85</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6,88; 24,23</t>
+          <t>7,19; 24,17</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 4,81</t>
+          <t>-2,43; 4,46</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 7,43</t>
+          <t>-1,12; 7,91</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,04; 15,76</t>
+          <t>4,75; 15,58</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 8,02</t>
+          <t>-0,25; 7,63</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 5,92</t>
+          <t>-1,39; 5,97</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-48,65; —</t>
+          <t>-59,47; —</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1893,17 +1893,17 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>71,72; 2792,17</t>
+          <t>102,88; 2505,17</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-49,03; 1489,42</t>
+          <t>-56,5; 1177,88</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-76,5; 923,54</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 6,06</t>
+          <t>-2,43; 6,38</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 5,42</t>
+          <t>-2,82; 5,68</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 7,78</t>
+          <t>-1,34; 8,13</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 7,83</t>
+          <t>-2,74; 7,23</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 6,36</t>
+          <t>-3,75; 6,44</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 10,57</t>
+          <t>-1,08; 10,22</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 5,24</t>
+          <t>-1,55; 5,16</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 5,25</t>
+          <t>-2,07; 4,87</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,38; 8,28</t>
+          <t>0,02; 7,56</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-53,67; 295,46</t>
+          <t>-48,5; 322,55</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-53,19; 254,17</t>
+          <t>-51,64; 258,32</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-30,72; 403,13</t>
+          <t>-29,51; 400,91</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-41,04; 209,19</t>
+          <t>-40,58; 197,83</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-44,49; 185,3</t>
+          <t>-46,45; 189,6</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-16,01; 284,78</t>
+          <t>-20,55; 277,22</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-29,47; 150,24</t>
+          <t>-26,2; 154,71</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-33,84; 150,62</t>
+          <t>-32,81; 138,06</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>0,69; 224,39</t>
+          <t>-1,97; 229,84</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-10,69; 0,1</t>
+          <t>-11,03; 0,32</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-6,03; 6,4</t>
+          <t>-5,0; 7,47</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-15,23; -5,81</t>
+          <t>-15,79; -5,69</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-7,94; 1,22</t>
+          <t>-8,09; 1,09</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 7,81</t>
+          <t>-2,57; 8,48</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-11,8; -3,88</t>
+          <t>-11,4; -3,25</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-7,9; -0,63</t>
+          <t>-8,32; -1,01</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 5,71</t>
+          <t>-3,31; 5,54</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-12,27; -6,14</t>
+          <t>-12,43; -6,12</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-69,09; 2,98</t>
+          <t>-69,53; 4,91</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-37,29; 71,08</t>
+          <t>-31,74; 78,53</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-96,08; -51,5</t>
+          <t>-100,0; -50,3</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-68,86; 22,36</t>
+          <t>-70,45; 23,31</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-27,1; 123,67</t>
+          <t>-22,7; 140,34</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-96,41; -42,19</t>
+          <t>-96,33; -38,73</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-60,89; -4,39</t>
+          <t>-64,41; -9,48</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-21,38; 63,39</t>
+          <t>-25,26; 63,63</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-94,19; -62,81</t>
+          <t>-94,04; -66,66</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 3,56</t>
+          <t>-1,73; 3,68</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 4,6</t>
+          <t>-0,39; 4,77</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-6,17; -1,59</t>
+          <t>-6,37; -2,0</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 3,78</t>
+          <t>-1,09; 4,02</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 4,34</t>
+          <t>-0,72; 4,18</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 0,32</t>
+          <t>-4,51; 0,36</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 3,03</t>
+          <t>-0,64; 2,88</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>0,03; 3,66</t>
+          <t>-0,04; 3,51</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-4,53; -1,35</t>
+          <t>-4,55; -1,36</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-15,29; 50,27</t>
+          <t>-18,44; 51,43</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-8,4; 61,07</t>
+          <t>-5,29; 65,8</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-64,09; -21,4</t>
+          <t>-65,93; -27,1</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-14,33; 55,0</t>
+          <t>-12,13; 58,14</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-7,84; 65,34</t>
+          <t>-8,44; 58,86</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-46,15; 5,79</t>
+          <t>-48,1; 5,51</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-6,94; 40,94</t>
+          <t>-7,07; 39,14</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 49,71</t>
+          <t>-0,43; 47,95</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-50,1; -17,91</t>
+          <t>-50,99; -18,58</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP2001-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP2001-Provincia-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6,77</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4,0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-6,16</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-0,52</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>7,99</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-5,11</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6,77</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>4,0</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-6,48</t>
+          <t>-4,58</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-5,81</t>
+          <t>-5,41</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,0; 7,77</t>
+          <t>-2,7; 16,94</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 18,72</t>
+          <t>-5,99; 13,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,82; 1,44</t>
+          <t>-14,84; -0,74</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 16,44</t>
+          <t>-8,61; 7,56</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 13,19</t>
+          <t>-1,05; 17,95</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-14,62; -1,19</t>
+          <t>-12,49; 1,93</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 9,88</t>
+          <t>-3,18; 10,29</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 12,09</t>
+          <t>-0,61; 13,02</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-11,96; -1,45</t>
+          <t>-11,0; -1,04</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>83,72%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>49,44%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-76,23%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-6,31%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>97,49%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-62,33%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>83,72%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>49,44%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-80,13%</t>
+          <t>-55,92%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-71,41%</t>
+          <t>-66,53%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-74,9; 278,53</t>
+          <t>-27,51; 405,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-25,54; 554,86</t>
+          <t>-53,64; 338,22</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 122,31</t>
+          <t>-100,0; 75,77</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-27,51; 486,42</t>
+          <t>-75,13; 205,74</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-49,46; 415,09</t>
+          <t>-17,5; 513,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 56,21</t>
+          <t>-100,0; 122,34</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-34,68; 195,78</t>
+          <t>-30,56; 205,61</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-17,85; 228,74</t>
+          <t>-11,03; 269,12</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-92,12; -9,56</t>
+          <t>-90,5; -9,47</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-5,57</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-10,01</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-10,92</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>1,85</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-4,28</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-10,18</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-5,57</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-10,01</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-11,12</t>
+          <t>-9,74</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-10,8</t>
+          <t>-10,32</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,67; 9,9</t>
+          <t>-13,92; 2,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,14; 2,48</t>
+          <t>-17,46; -2,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-16,66; -4,61</t>
+          <t>-17,78; -2,92</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-12,75; 3,23</t>
+          <t>-5,62; 9,89</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-17,44; -3,08</t>
+          <t>-11,84; 2,24</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-18,33; -3,03</t>
+          <t>-15,83; -3,39</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-7,89; 3,49</t>
+          <t>-8,13; 3,69</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-12,57; -1,73</t>
+          <t>-13,22; -2,58</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-16,48; -6,08</t>
+          <t>-15,96; -5,93</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-30,83%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-55,36%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-60,4%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>15,01%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-34,79%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-82,64%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-30,83%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-55,36%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-61,5%</t>
+          <t>-79,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-70,41%</t>
+          <t>-67,28%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-41,84; 115,67</t>
+          <t>-61,45; 20,7</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-73,07; 33,15</t>
+          <t>-78,1; -14,14</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-96,88; -49,32</t>
+          <t>-82,27; -14,67</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-58,02; 30,0</t>
+          <t>-37,06; 105,36</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-77,93; -18,37</t>
+          <t>-71,06; 31,19</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-83,38; -12,51</t>
+          <t>-94,9; -26,68</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-42,26; 29,4</t>
+          <t>-45,13; 28,77</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-67,6; -12,87</t>
+          <t>-69,26; -17,56</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-86,5; -42,68</t>
+          <t>-82,91; -39,04</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>2,17</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-0,64</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>4,45</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>5,17</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>2,09</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>6,2</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2,17</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-0,64</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,6</t>
+          <t>6,23</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5,9</t>
+          <t>5,32</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 12,86</t>
+          <t>-2,9; 8,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 8,48</t>
+          <t>-4,82; 3,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,64; 13,17</t>
+          <t>-1,64; 11,7</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 8,94</t>
+          <t>0,14; 12,07</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,82; 4,39</t>
+          <t>-1,95; 9,21</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 14,32</t>
+          <t>0,72; 13,7</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 8,62</t>
+          <t>-0,17; 8,3</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 4,35</t>
+          <t>-2,42; 4,41</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,48; 11,3</t>
+          <t>1,02; 10,09</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>75,59%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-22,25%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>155,04%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>241,79%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>97,66%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>289,87%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>75,59%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-22,25%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>195,08%</t>
+          <t>291,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>235,26%</t>
+          <t>212,18%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-49,68; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>-60,2; —</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>-46,56; —</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
           <t>-100,0; —</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>-51,02; —</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-43,87; —</t>
+          <t>-29,36; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-24,08; 897,82</t>
+          <t>-19,77; 764,63</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-76,26; 487,65</t>
+          <t>-73,57; 450,86</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>14,08; 1064,8</t>
+          <t>2,2; 909,85</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>6,72</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>14,34</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1,68</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>6,53</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>14,6</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-0,25</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>6,72</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>14,34</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,34</t>
+          <t>-0,13</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,58</t>
+          <t>0,79</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 14,54</t>
+          <t>0,22; 14,84</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,33; 24,65</t>
+          <t>6,81; 23,58</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,91; 6,54</t>
+          <t>-4,41; 10,88</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 14,48</t>
+          <t>-1,15; 13,63</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,3; 22,64</t>
+          <t>5,9; 23,25</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 10,37</t>
+          <t>-5,82; 5,88</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,71; 11,9</t>
+          <t>1,94; 12,31</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8,86; 20,71</t>
+          <t>8,49; 20,46</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 5,44</t>
+          <t>-3,59; 5,9</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>168,86%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>360,38%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>42,32%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>131,11%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>293,13%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-4,93%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>168,86%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>360,38%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>-2,66%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>17,71%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-27,98; 586,42</t>
+          <t>-19,27; 1052,91</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>52,56; 961,94</t>
+          <t>58,13; 1713,67</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-81,4; 327,28</t>
+          <t>-100,0; 816,77</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-21,23; 986,63</t>
+          <t>-28,55; 567,98</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>56,81; 1643,8</t>
+          <t>45,56; 978,11</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 676,21</t>
+          <t>-83,21; 247,41</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,27; 391,94</t>
+          <t>16,56; 437,76</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>127,39; 766,79</t>
+          <t>115,05; 788,71</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-63,14; 183,14</t>
+          <t>-63,69; 229,44</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>1,01</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>7,76</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>4,15</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>0,03</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-10,46</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-15,22</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1,01</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>7,76</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,77</t>
+          <t>-15,29</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-5,3</t>
+          <t>-5,25</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-16,18; 15,2</t>
+          <t>-10,69; 11,03</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-24,36; 2,74</t>
+          <t>-4,94; 18,93</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-28,73; -2,93</t>
+          <t>-6,2; 15,31</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-10,0; 12,23</t>
+          <t>-14,49; 15,24</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 20,3</t>
+          <t>-24,05; 3,01</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-7,18; 15,0</t>
+          <t>-27,37; -2,07</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-8,81; 10,26</t>
+          <t>-8,42; 10,89</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-9,53; 8,1</t>
+          <t>-10,75; 7,93</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-14,0; 3,06</t>
+          <t>-13,38; 3,5</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>9,87%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>76,15%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>40,71%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>0,12%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-47,54%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-69,17%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>9,87%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>76,15%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>-69,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-33,16%</t>
+          <t>-32,83%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-54,51; 108,89</t>
+          <t>-72,13; 221,39</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-81,8; 27,81</t>
+          <t>-41,24; 395,05</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-91,0; -11,33</t>
+          <t>-45,72; 378,3</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-70,53; 251,46</t>
+          <t>-50,93; 113,27</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-29,64; 400,78</t>
+          <t>-81,43; 29,9</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-52,14; 320,87</t>
+          <t>-90,29; -3,54</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-44,46; 94,08</t>
+          <t>-41,81; 100,41</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-48,15; 78,41</t>
+          <t>-51,26; 74,72</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-68,03; 30,33</t>
+          <t>-65,76; 36,19</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>14,12</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>0,38</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>1,49</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>4,06</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>6,11</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>2,16</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>14,12</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>0,38</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,63</t>
+          <t>2,09</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1,82</t>
+          <t>1,78</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 11,0</t>
+          <t>6,84; 24,31</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 15,07</t>
+          <t>-2,17; 4,77</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 10,85</t>
+          <t>-2,17; 6,67</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7,19; 24,17</t>
+          <t>-1,76; 11,82</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 4,46</t>
+          <t>-1,08; 14,6</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 7,91</t>
+          <t>-3,26; 8,71</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,75; 15,58</t>
+          <t>4,52; 16,52</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 7,63</t>
+          <t>-0,56; 7,55</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 5,97</t>
+          <t>-1,45; 6,13</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>1303,98%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>35,22%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>137,37%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>162,04%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>244,28%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>86,35%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>1303,98%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>35,22%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>150,25%</t>
+          <t>83,61%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>102,65%</t>
+          <t>100,55%</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-59,47; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1883,22 +1883,22 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
+          <t>-65,33; —</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>102,88; 2505,17</t>
+          <t>69,31; 2339,3</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-56,5; 1177,88</t>
+          <t>-62,3; 1187,22</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>1,93</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>1,48</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>5,62</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>1,52</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>1,1</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>2,97</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>1,93</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>1,48</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,42</t>
+          <t>3,25</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>3,87</t>
+          <t>4,58</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 6,38</t>
+          <t>-3,07; 7,69</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 5,68</t>
+          <t>-3,1; 6,99</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 8,13</t>
+          <t>-0,32; 11,84</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 7,23</t>
+          <t>-3,38; 5,93</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 6,44</t>
+          <t>-3,37; 5,31</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 10,22</t>
+          <t>-1,37; 8,6</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 5,16</t>
+          <t>-1,72; 5,68</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 4,87</t>
+          <t>-1,75; 4,75</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,02; 7,56</t>
+          <t>0,44; 8,83</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>33,14%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>25,34%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>96,42%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>37,22%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>27,02%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>72,67%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>33,14%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>25,34%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>75,9%</t>
+          <t>79,66%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>77,85%</t>
+          <t>92,18%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-48,5; 322,55</t>
+          <t>-43,56; 212,48</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-51,64; 258,32</t>
+          <t>-43,34; 215,93</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-29,51; 400,91</t>
+          <t>-6,29; 318,76</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-40,58; 197,83</t>
+          <t>-59,9; 292,45</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-46,45; 189,6</t>
+          <t>-57,38; 283,81</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-20,55; 277,22</t>
+          <t>-31,99; 449,87</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-26,2; 154,71</t>
+          <t>-29,95; 166,99</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-32,81; 138,06</t>
+          <t>-28,31; 143,92</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 229,84</t>
+          <t>1,63; 252,46</t>
         </is>
       </c>
     </row>
@@ -2136,34 +2136,34 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>-3,41</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>2,48</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>-7,65</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>-5,25</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>0,64</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>-10,54</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>-3,41</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>2,48</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>-7,47</t>
-        </is>
-      </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
           <t>-4,33</t>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-9,0</t>
+          <t>-9,1</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-11,03; 0,32</t>
+          <t>-8,34; 0,94</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 7,47</t>
+          <t>-3,34; 8,1</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-15,79; -5,69</t>
+          <t>-12,2; -3,94</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-8,09; 1,09</t>
+          <t>-10,73; 0,02</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 8,48</t>
+          <t>-5,85; 6,24</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-11,4; -3,25</t>
+          <t>-15,58; -6,04</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-8,32; -1,01</t>
+          <t>-7,84; -0,77</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 5,54</t>
+          <t>-2,42; 5,31</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-12,43; -6,12</t>
+          <t>-12,46; -5,87</t>
         </is>
       </c>
     </row>
@@ -2242,32 +2242,32 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>-38,06%</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>27,66%</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>-85,29%</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>-42,03%</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>5,11%</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>-84,42%</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>-38,06%</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>27,66%</t>
-        </is>
-      </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-83,24%</t>
+          <t>-84,47%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-84,09%</t>
+          <t>-84,98%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-69,53; 4,91</t>
+          <t>-73,12; 18,49</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-31,74; 78,53</t>
+          <t>-31,2; 129,77</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -50,3</t>
+          <t>-97,29; -49,62</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-70,45; 23,31</t>
+          <t>-67,49; 11,74</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-22,7; 140,34</t>
+          <t>-37,55; 70,55</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-96,33; -38,73</t>
+          <t>-96,26; -52,26</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-64,41; -9,48</t>
+          <t>-60,5; -6,51</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-25,26; 63,63</t>
+          <t>-19,88; 60,71</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-94,04; -66,66</t>
+          <t>-94,21; -62,22</t>
         </is>
       </c>
     </row>
@@ -2352,32 +2352,32 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>1,43</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>1,73</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>-1,8</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>0,89</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>2,06</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>-4,09</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>1,43</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>1,73</t>
-        </is>
-      </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>-1,98</t>
+          <t>-3,84</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-2,98</t>
+          <t>-2,77</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 3,68</t>
+          <t>-1,1; 3,8</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 4,77</t>
+          <t>-0,7; 4,16</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-6,37; -2,0</t>
+          <t>-3,92; 0,63</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 4,02</t>
+          <t>-1,54; 3,33</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 4,18</t>
+          <t>-0,77; 4,59</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 0,36</t>
+          <t>-5,93; -1,8</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 2,88</t>
+          <t>-0,66; 3,0</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 3,51</t>
+          <t>0,03; 3,81</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-4,55; -1,36</t>
+          <t>-4,38; -0,99</t>
         </is>
       </c>
     </row>
@@ -2458,32 +2458,32 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>17,89%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>21,67%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>-22,58%</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>10,52%</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>24,4%</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>-48,49%</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>17,89%</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>21,67%</t>
-        </is>
-      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-24,84%</t>
+          <t>-45,44%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-36,29%</t>
+          <t>-33,78%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-18,44; 51,43</t>
+          <t>-12,22; 54,55</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 65,8</t>
+          <t>-8,08; 60,9</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-65,93; -27,1</t>
+          <t>-44,79; 9,5</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-12,13; 58,14</t>
+          <t>-16,21; 45,07</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-8,44; 58,86</t>
+          <t>-7,86; 62,88</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-48,1; 5,51</t>
+          <t>-62,86; -22,68</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-7,07; 39,14</t>
+          <t>-7,15; 40,73</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 47,95</t>
+          <t>1,32; 51,64</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-50,99; -18,58</t>
+          <t>-47,96; -13,35</t>
         </is>
       </c>
     </row>
